--- a/database/excels/system/base-seeder.xlsx
+++ b/database/excels/system/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D7E637-73E3-F04A-B228-8D048D4A461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BFB7EE-6746-DE4E-BE1F-DDCBDBACD941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="2120" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="4880" yWindow="2120" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="roles" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="70">
   <si>
     <t>name</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>cyan</t>
+  </si>
+  <si>
+    <t>view, create, show, update, delete, restore, destroy, search</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1048,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -1078,7 +1081,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1089,7 +1092,7 @@
         <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1100,7 +1103,7 @@
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1111,7 +1114,7 @@
         <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1122,7 +1125,7 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1133,7 +1136,7 @@
         <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">

--- a/database/excels/system/base-seeder.xlsx
+++ b/database/excels/system/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BFB7EE-6746-DE4E-BE1F-DDCBDBACD941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5339C265-71E9-C542-97AD-7025B31014DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="2120" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="4880" yWindow="2120" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="roles" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t>system</t>
   </si>
   <si>
-    <t>supervised_user_circle</t>
-  </si>
-  <si>
     <t>Account Manajemen System</t>
   </si>
   <si>
@@ -241,6 +238,9 @@
   </si>
   <si>
     <t>view, create, show, update, delete, restore, destroy, search</t>
+  </si>
+  <si>
+    <t>local_police</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>11</v>
@@ -711,16 +711,16 @@
         <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +743,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -761,16 +761,16 @@
         <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -778,19 +778,19 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="4" t="b">
         <v>1</v>
@@ -804,22 +804,22 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
         <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
       </c>
       <c r="H3" s="4" t="b">
         <v>1</v>
@@ -833,22 +833,22 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H4" s="4" t="b">
         <v>1</v>
@@ -862,20 +862,20 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
       <c r="H5" s="4" t="b">
         <v>0</v>
       </c>
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -891,20 +891,20 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>40</v>
-      </c>
       <c r="H6" s="4" t="b">
         <v>0</v>
       </c>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -920,23 +920,23 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
       <c r="H7" s="4" t="b">
         <v>0</v>
       </c>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -952,22 +952,22 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
         <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>48</v>
       </c>
       <c r="H8" s="4" t="b">
         <v>1</v>
@@ -981,23 +981,23 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
         <v>52</v>
       </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>53</v>
-      </c>
       <c r="H9" s="4" t="b">
         <v>0</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1013,22 +1013,22 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="s">
         <v>54</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>55</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" t="s">
         <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
       </c>
       <c r="H10" s="4" t="b">
         <v>1</v>
@@ -1053,13 +1053,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1067,10 +1067,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1078,10 +1078,10 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1089,10 +1089,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1100,10 +1100,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1111,10 +1111,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1122,10 +1122,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1133,10 +1133,10 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1144,10 +1144,10 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1155,10 +1155,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1177,10 +1177,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -1215,13 +1215,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
@@ -1229,10 +1229,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -1240,10 +1240,10 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1251,10 +1251,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1262,10 +1262,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1273,10 +1273,10 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1284,10 +1284,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1295,10 +1295,10 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1306,10 +1306,10 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1317,10 +1317,10 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1339,16 +1339,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1356,13 +1356,13 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1370,13 +1370,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1384,13 +1384,13 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1398,13 +1398,13 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1412,13 +1412,13 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1426,13 +1426,13 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1440,13 +1440,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1454,13 +1454,13 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1468,13 +1468,13 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/database/excels/system/base-seeder.xlsx
+++ b/database/excels/system/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5339C265-71E9-C542-97AD-7025B31014DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{339450B8-CC72-264D-A25D-57A448E5757D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4880" yWindow="2120" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="4880" yWindow="2120" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="roles" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="71">
   <si>
     <t>name</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>local_police</t>
+  </si>
+  <si>
+    <t>title</t>
   </si>
 </sst>
 </file>
@@ -730,18 +733,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.83203125" style="4"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.83203125" style="4"/>
+    <col min="11" max="11" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -749,57 +752,60 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
       <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="I2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="4" t="b">
+      <c r="J2" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -807,28 +813,31 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
       <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="I3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I3" s="4" t="b">
+      <c r="J3" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -836,28 +845,31 @@
         <v>29</v>
       </c>
       <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
       <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="I4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="4" t="b">
+      <c r="J4" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -865,28 +877,31 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
       <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
         <v>35</v>
-      </c>
-      <c r="H5" s="4" t="b">
-        <v>0</v>
       </c>
       <c r="I5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -894,28 +909,31 @@
         <v>36</v>
       </c>
       <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>38</v>
       </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" t="s">
         <v>39</v>
-      </c>
-      <c r="H6" s="4" t="b">
-        <v>0</v>
       </c>
       <c r="I6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -923,31 +941,34 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
       <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
         <v>43</v>
-      </c>
-      <c r="H7" s="4" t="b">
-        <v>0</v>
       </c>
       <c r="I7" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -955,28 +976,31 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>27</v>
       </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
       <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="4" t="b">
+      <c r="I8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="4" t="b">
+      <c r="J8" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -984,31 +1008,34 @@
         <v>48</v>
       </c>
       <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
         <v>49</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>50</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>51</v>
       </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
       <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
         <v>52</v>
-      </c>
-      <c r="H9" s="4" t="b">
-        <v>0</v>
       </c>
       <c r="I9" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1016,24 +1043,27 @@
         <v>53</v>
       </c>
       <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
         <v>54</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>55</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>51</v>
       </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
       <c r="G10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="4" t="b">
+      <c r="I10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="4" t="b">
+      <c r="J10" s="4" t="b">
         <v>0</v>
       </c>
     </row>
